--- a/artfynd/A 24796-2024 artfynd.xlsx
+++ b/artfynd/A 24796-2024 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129092672</v>
       </c>
       <c r="B5" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24796-2024 artfynd.xlsx
+++ b/artfynd/A 24796-2024 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>129092672</v>
       </c>
       <c r="B5" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
